--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/117.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/117.xlsx
@@ -426,13 +426,13 @@
         <v>-1.927303588871902</v>
       </c>
       <c r="E2">
-        <v>-10.8378992928369</v>
+        <v>-9.484696161390836</v>
       </c>
       <c r="F2">
-        <v>-7.637423214089022</v>
+        <v>-7.312070234159452</v>
       </c>
       <c r="G2">
-        <v>-11.14140711435223</v>
+        <v>-10.21425904116948</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.716074907350211</v>
       </c>
       <c r="E3">
-        <v>-11.64960108786777</v>
+        <v>-10.92942428100593</v>
       </c>
       <c r="F3">
-        <v>-7.505230489474334</v>
+        <v>-6.985074159342613</v>
       </c>
       <c r="G3">
-        <v>-11.74152294643807</v>
+        <v>-10.6777486588496</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.650483268353584</v>
       </c>
       <c r="E4">
-        <v>-11.237057105769</v>
+        <v>-11.28492760450408</v>
       </c>
       <c r="F4">
-        <v>-7.40430011963042</v>
+        <v>-7.218707603032466</v>
       </c>
       <c r="G4">
-        <v>-11.23311915742666</v>
+        <v>-10.4239059585349</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.543570414136237</v>
       </c>
       <c r="E5">
-        <v>-13.46706337458019</v>
+        <v>-12.92804817039521</v>
       </c>
       <c r="F5">
-        <v>-7.500026035909721</v>
+        <v>-7.265469291671168</v>
       </c>
       <c r="G5">
-        <v>-11.72177554229632</v>
+        <v>-10.16133334963315</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.342178154889822</v>
       </c>
       <c r="E6">
-        <v>-13.0552711191667</v>
+        <v>-13.27454888756611</v>
       </c>
       <c r="F6">
-        <v>-7.514721243099084</v>
+        <v>-7.356832494079911</v>
       </c>
       <c r="G6">
-        <v>-11.88743855162699</v>
+        <v>-10.54179779573389</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.961316303925845</v>
       </c>
       <c r="E7">
-        <v>-15.26102288119281</v>
+        <v>-13.42714487620258</v>
       </c>
       <c r="F7">
-        <v>-7.429738791823645</v>
+        <v>-7.066995703009986</v>
       </c>
       <c r="G7">
-        <v>-12.1077056990824</v>
+        <v>-10.3669778174416</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.358468876072835</v>
       </c>
       <c r="E8">
-        <v>-15.65266795574619</v>
+        <v>-15.81656248703179</v>
       </c>
       <c r="F8">
-        <v>-7.342038305270834</v>
+        <v>-7.074809707996764</v>
       </c>
       <c r="G8">
-        <v>-11.59761684239149</v>
+        <v>-11.30622262402484</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.496129687384245</v>
       </c>
       <c r="E9">
-        <v>-16.01603271012165</v>
+        <v>-15.29812466873766</v>
       </c>
       <c r="F9">
-        <v>-7.667130765577315</v>
+        <v>-6.723469697700748</v>
       </c>
       <c r="G9">
-        <v>-12.24028311629359</v>
+        <v>-10.22079736860954</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.371546873555038</v>
       </c>
       <c r="E10">
-        <v>-18.53959277800607</v>
+        <v>-17.82856348863973</v>
       </c>
       <c r="F10">
-        <v>-7.524222290812284</v>
+        <v>-6.922105220291783</v>
       </c>
       <c r="G10">
-        <v>-11.23994219178309</v>
+        <v>-10.11059261815274</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.000094942377751</v>
       </c>
       <c r="E11">
-        <v>-17.87904238840323</v>
+        <v>-17.39754786106367</v>
       </c>
       <c r="F11">
-        <v>-7.57083986221268</v>
+        <v>-6.923507195953426</v>
       </c>
       <c r="G11">
-        <v>-11.09808200487978</v>
+        <v>-10.40599590716745</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.42281314077081</v>
       </c>
       <c r="E12">
-        <v>-18.26843681137479</v>
+        <v>-17.27219064358334</v>
       </c>
       <c r="F12">
-        <v>-7.661204933968219</v>
+        <v>-7.338857036013195</v>
       </c>
       <c r="G12">
-        <v>-11.38021331682755</v>
+        <v>-9.294725222727051</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.69236862778678</v>
       </c>
       <c r="E13">
-        <v>-19.17078054214318</v>
+        <v>-18.71462282687654</v>
       </c>
       <c r="F13">
-        <v>-7.687863455642811</v>
+        <v>-6.922732367834297</v>
       </c>
       <c r="G13">
-        <v>-10.28420093677766</v>
+        <v>-9.001023554119529</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.875031982833802</v>
       </c>
       <c r="E14">
-        <v>-20.02628626625025</v>
+        <v>-20.35029858149906</v>
       </c>
       <c r="F14">
-        <v>-7.745739196469588</v>
+        <v>-7.028074942358625</v>
       </c>
       <c r="G14">
-        <v>-9.59125740777065</v>
+        <v>-7.394478704276468</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.041920405077045</v>
       </c>
       <c r="E15">
-        <v>-21.01442193709396</v>
+        <v>-20.82845109502096</v>
       </c>
       <c r="F15">
-        <v>-7.876555284717281</v>
+        <v>-7.179791593498851</v>
       </c>
       <c r="G15">
-        <v>-8.852313848495466</v>
+        <v>-8.31284390014353</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.26100771860875</v>
       </c>
       <c r="E16">
-        <v>-21.61732938105316</v>
+        <v>-19.84862970245533</v>
       </c>
       <c r="F16">
-        <v>-7.622676536457408</v>
+        <v>-7.002357141997804</v>
       </c>
       <c r="G16">
-        <v>-8.317273410075076</v>
+        <v>-6.685124801031291</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.588297755180677</v>
       </c>
       <c r="E17">
-        <v>-22.56273889963451</v>
+        <v>-22.21096251024467</v>
       </c>
       <c r="F17">
-        <v>-7.636810715826226</v>
+        <v>-7.247780088448667</v>
       </c>
       <c r="G17">
-        <v>-7.809018595612927</v>
+        <v>-5.272581230335061</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.062952017386834</v>
       </c>
       <c r="E18">
-        <v>-23.29574487336007</v>
+        <v>-22.98187633988844</v>
       </c>
       <c r="F18">
-        <v>-7.461589097415526</v>
+        <v>-6.623811043706932</v>
       </c>
       <c r="G18">
-        <v>-6.724864589684703</v>
+        <v>-5.373893855473377</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7010282338996251</v>
       </c>
       <c r="E19">
-        <v>-24.50033707329642</v>
+        <v>-24.68958200207697</v>
       </c>
       <c r="F19">
-        <v>-7.085731339916114</v>
+        <v>-6.306873481085528</v>
       </c>
       <c r="G19">
-        <v>-7.049403989990536</v>
+        <v>-5.436923331995562</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4934796745971852</v>
       </c>
       <c r="E20">
-        <v>-26.0449542725727</v>
+        <v>-24.43034497903387</v>
       </c>
       <c r="F20">
-        <v>-6.953243254148195</v>
+        <v>-6.122280282920216</v>
       </c>
       <c r="G20">
-        <v>-5.461990782818923</v>
+        <v>-5.233033453322927</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.4176987242249436</v>
       </c>
       <c r="E21">
-        <v>-26.05541051905642</v>
+        <v>-25.04355017288652</v>
       </c>
       <c r="F21">
-        <v>-6.861755334898611</v>
+        <v>-5.908486715086031</v>
       </c>
       <c r="G21">
-        <v>-5.840005425220603</v>
+        <v>-5.166180296702885</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.4380791395020735</v>
       </c>
       <c r="E22">
-        <v>-26.77696398201659</v>
+        <v>-27.14476211244557</v>
       </c>
       <c r="F22">
-        <v>-6.328286768768185</v>
+        <v>-5.813561758073464</v>
       </c>
       <c r="G22">
-        <v>-5.566223309122877</v>
+        <v>-3.629233045731922</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.51375848515823</v>
       </c>
       <c r="E23">
-        <v>-27.86857528393556</v>
+        <v>-25.7802830807204</v>
       </c>
       <c r="F23">
-        <v>-6.319409305259189</v>
+        <v>-5.665831294722399</v>
       </c>
       <c r="G23">
-        <v>-5.719094370489802</v>
+        <v>-3.939020655114763</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6094449475924483</v>
       </c>
       <c r="E24">
-        <v>-27.62455393355824</v>
+        <v>-26.94141551560514</v>
       </c>
       <c r="F24">
-        <v>-6.086756967383952</v>
+        <v>-5.232695645379287</v>
       </c>
       <c r="G24">
-        <v>-5.31928309625756</v>
+        <v>-4.488263333898628</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6995417108243313</v>
       </c>
       <c r="E25">
-        <v>-27.67055870100216</v>
+        <v>-28.17874858261694</v>
       </c>
       <c r="F25">
-        <v>-5.8800496916684</v>
+        <v>-5.314509892970889</v>
       </c>
       <c r="G25">
-        <v>-5.388801242036716</v>
+        <v>-3.902458990179052</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.7667114751410193</v>
       </c>
       <c r="E26">
-        <v>-27.64103305047215</v>
+        <v>-28.15961577993453</v>
       </c>
       <c r="F26">
-        <v>-5.936531771289591</v>
+        <v>-5.004478871846716</v>
       </c>
       <c r="G26">
-        <v>-6.950428610002945</v>
+        <v>-4.311903951930574</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8034730684932267</v>
       </c>
       <c r="E27">
-        <v>-28.32317973261758</v>
+        <v>-27.93886172900861</v>
       </c>
       <c r="F27">
-        <v>-5.92073509663604</v>
+        <v>-4.808973543997547</v>
       </c>
       <c r="G27">
-        <v>-6.619026448794203</v>
+        <v>-5.86096117848419</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8124189849401903</v>
       </c>
       <c r="E28">
-        <v>-28.97369955229343</v>
+        <v>-27.48888538076244</v>
       </c>
       <c r="F28">
-        <v>-6.027880720345096</v>
+        <v>-5.183531078940385</v>
       </c>
       <c r="G28">
-        <v>-6.509967147093992</v>
+        <v>-4.668582128331651</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.8016788754450761</v>
       </c>
       <c r="E29">
-        <v>-28.20016826467322</v>
+        <v>-29.32788508985535</v>
       </c>
       <c r="F29">
-        <v>-5.591390781873083</v>
+        <v>-4.771806341721057</v>
       </c>
       <c r="G29">
-        <v>-6.692378206307835</v>
+        <v>-5.367527676401359</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7819938794904085</v>
       </c>
       <c r="E30">
-        <v>-27.60366861143486</v>
+        <v>-26.88670702111847</v>
       </c>
       <c r="F30">
-        <v>-5.264768857578767</v>
+        <v>-5.246739949437404</v>
       </c>
       <c r="G30">
-        <v>-6.361863271303617</v>
+        <v>-4.754762249809959</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7653042610122954</v>
       </c>
       <c r="E31">
-        <v>-28.20533072504196</v>
+        <v>-27.27269150316225</v>
       </c>
       <c r="F31">
-        <v>-5.902897025057488</v>
+        <v>-4.812546384542779</v>
       </c>
       <c r="G31">
-        <v>-6.939649473727078</v>
+        <v>-5.7984117310652</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7649360267408887</v>
       </c>
       <c r="E32">
-        <v>-27.43971068151315</v>
+        <v>-25.92642599389594</v>
       </c>
       <c r="F32">
-        <v>-5.734610058924019</v>
+        <v>-5.022295563395411</v>
       </c>
       <c r="G32">
-        <v>-6.867631866065772</v>
+        <v>-5.44433564345799</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7936417400015119</v>
       </c>
       <c r="E33">
-        <v>-26.75791722034032</v>
+        <v>-25.06952097132051</v>
       </c>
       <c r="F33">
-        <v>-5.409142656242058</v>
+        <v>-5.079249587379402</v>
       </c>
       <c r="G33">
-        <v>-7.084197823608275</v>
+        <v>-5.416331738741294</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8616204559651147</v>
       </c>
       <c r="E34">
-        <v>-26.73030711431556</v>
+        <v>-27.01626213400391</v>
       </c>
       <c r="F34">
-        <v>-5.705318626165009</v>
+        <v>-5.33328631030434</v>
       </c>
       <c r="G34">
-        <v>-6.474024554174124</v>
+        <v>-5.906924792751431</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9762027873643195</v>
       </c>
       <c r="E35">
-        <v>-26.4269899252818</v>
+        <v>-25.69368960074573</v>
       </c>
       <c r="F35">
-        <v>-5.80432954443941</v>
+        <v>-5.001773110290189</v>
       </c>
       <c r="G35">
-        <v>-6.625551534052106</v>
+        <v>-5.545611852595374</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.142698131388559</v>
       </c>
       <c r="E36">
-        <v>-25.84796112476504</v>
+        <v>-25.3882666712984</v>
       </c>
       <c r="F36">
-        <v>-5.843456582786256</v>
+        <v>-4.913219402175434</v>
       </c>
       <c r="G36">
-        <v>-6.623267257630009</v>
+        <v>-5.590847146843975</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.36072441489016</v>
       </c>
       <c r="E37">
-        <v>-26.55375096970451</v>
+        <v>-25.4237472651485</v>
       </c>
       <c r="F37">
-        <v>-5.808820934415596</v>
+        <v>-5.247097075121336</v>
       </c>
       <c r="G37">
-        <v>-6.341030008224983</v>
+        <v>-5.263758626472904</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.625000962597964</v>
       </c>
       <c r="E38">
-        <v>-26.32420715072971</v>
+        <v>-24.81158362031761</v>
       </c>
       <c r="F38">
-        <v>-5.972056670531771</v>
+        <v>-5.359362820055008</v>
       </c>
       <c r="G38">
-        <v>-6.143016347884556</v>
+        <v>-5.310973626953989</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.929395005072102</v>
       </c>
       <c r="E39">
-        <v>-25.56973168173377</v>
+        <v>-24.32518022715374</v>
       </c>
       <c r="F39">
-        <v>-5.683551380210251</v>
+        <v>-4.769038023780869</v>
       </c>
       <c r="G39">
-        <v>-6.274471490157937</v>
+        <v>-4.772126061163436</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.264173422595413</v>
       </c>
       <c r="E40">
-        <v>-24.59676639881576</v>
+        <v>-22.07410749725886</v>
       </c>
       <c r="F40">
-        <v>-5.647492772074568</v>
+        <v>-4.88356450890883</v>
       </c>
       <c r="G40">
-        <v>-6.355371291501106</v>
+        <v>-4.565958527159784</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.616186306220329</v>
       </c>
       <c r="E41">
-        <v>-24.74085338479181</v>
+        <v>-22.82170421423714</v>
       </c>
       <c r="F41">
-        <v>-6.133454515933078</v>
+        <v>-5.099190820413657</v>
       </c>
       <c r="G41">
-        <v>-6.331393010160165</v>
+        <v>-4.346912971008366</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.971842113112686</v>
       </c>
       <c r="E42">
-        <v>-24.05885614228864</v>
+        <v>-21.95923369710628</v>
       </c>
       <c r="F42">
-        <v>-6.092234610218978</v>
+        <v>-5.087743794056861</v>
       </c>
       <c r="G42">
-        <v>-6.432566592385832</v>
+        <v>-5.147776974050077</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.31906704093544</v>
       </c>
       <c r="E43">
-        <v>-23.46220704940803</v>
+        <v>-21.554062070692</v>
       </c>
       <c r="F43">
-        <v>-5.974547048083799</v>
+        <v>-5.073495191935653</v>
       </c>
       <c r="G43">
-        <v>-6.366984685252869</v>
+        <v>-5.111526500395057</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.643445826901321</v>
       </c>
       <c r="E44">
-        <v>-22.55366836619714</v>
+        <v>-21.82591089384646</v>
       </c>
       <c r="F44">
-        <v>-5.922052739957685</v>
+        <v>-5.226337066128798</v>
       </c>
       <c r="G44">
-        <v>-6.324394516890146</v>
+        <v>-5.613279403418077</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.929947844934328</v>
       </c>
       <c r="E45">
-        <v>-23.17478027566719</v>
+        <v>-20.22034043442694</v>
       </c>
       <c r="F45">
-        <v>-5.837014858975206</v>
+        <v>-5.404668687030941</v>
       </c>
       <c r="G45">
-        <v>-5.963194135282423</v>
+        <v>-5.536560821091006</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.168094527787617</v>
       </c>
       <c r="E46">
-        <v>-22.09918165783933</v>
+        <v>-21.01904098058178</v>
       </c>
       <c r="F46">
-        <v>-5.683532375739266</v>
+        <v>-5.038538843117116</v>
       </c>
       <c r="G46">
-        <v>-6.158198509727653</v>
+        <v>-5.094113030858491</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.349282445263572</v>
       </c>
       <c r="E47">
-        <v>-20.81042776847043</v>
+        <v>-18.87877095270658</v>
       </c>
       <c r="F47">
-        <v>-5.6134153800391</v>
+        <v>-4.944712978009862</v>
       </c>
       <c r="G47">
-        <v>-6.876007546280129</v>
+        <v>-5.479182445804359</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.467394426927141</v>
       </c>
       <c r="E48">
-        <v>-20.30926155004155</v>
+        <v>-19.28613888901458</v>
       </c>
       <c r="F48">
-        <v>-5.840141886305242</v>
+        <v>-5.011743330880837</v>
       </c>
       <c r="G48">
-        <v>-5.566858933866416</v>
+        <v>-6.168444648171698</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.521851824227526</v>
       </c>
       <c r="E49">
-        <v>-19.81581637979575</v>
+        <v>-18.71239481766477</v>
       </c>
       <c r="F49">
-        <v>-5.456836751738475</v>
+        <v>-5.549902438006316</v>
       </c>
       <c r="G49">
-        <v>-5.990777600715631</v>
+        <v>-4.785715850602144</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.517554902104602</v>
       </c>
       <c r="E50">
-        <v>-20.92967154604041</v>
+        <v>-18.08451283955326</v>
       </c>
       <c r="F50">
-        <v>-6.035477757621459</v>
+        <v>-5.193215440613297</v>
       </c>
       <c r="G50">
-        <v>-7.255313301442125</v>
+        <v>-5.614236151078926</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.461182174137257</v>
       </c>
       <c r="E51">
-        <v>-18.89055857054855</v>
+        <v>-18.63331860454283</v>
       </c>
       <c r="F51">
-        <v>-5.607603179329437</v>
+        <v>-5.212677602608133</v>
       </c>
       <c r="G51">
-        <v>-7.036386924930121</v>
+        <v>-4.957711933549439</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.361571094431194</v>
       </c>
       <c r="E52">
-        <v>-18.85153671002445</v>
+        <v>-18.2989632546605</v>
       </c>
       <c r="F52">
-        <v>-5.857097041835937</v>
+        <v>-5.291744120436447</v>
       </c>
       <c r="G52">
-        <v>-6.586404333050225</v>
+        <v>-5.544181696922409</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.231264628935901</v>
       </c>
       <c r="E53">
-        <v>-17.66539351319535</v>
+        <v>-16.89860512337256</v>
       </c>
       <c r="F53">
-        <v>-6.044121624507928</v>
+        <v>-4.795065438648159</v>
       </c>
       <c r="G53">
-        <v>-6.178750376435449</v>
+        <v>-5.301644509624323</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.082178617721661</v>
       </c>
       <c r="E54">
-        <v>-17.81340668613606</v>
+        <v>-17.04433141693939</v>
       </c>
       <c r="F54">
-        <v>-5.67652289335753</v>
+        <v>-5.476412148706264</v>
       </c>
       <c r="G54">
-        <v>-7.11220503887051</v>
+        <v>-6.021297520042173</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.924119007404538</v>
       </c>
       <c r="E55">
-        <v>-17.58382663936919</v>
+        <v>-15.23558644269173</v>
       </c>
       <c r="F55">
-        <v>-5.644495608629599</v>
+        <v>-4.897140827868935</v>
       </c>
       <c r="G55">
-        <v>-7.357576053150212</v>
+        <v>-5.594806559308943</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.768088553534998</v>
       </c>
       <c r="E56">
-        <v>-16.19480780699647</v>
+        <v>-14.6572278563281</v>
       </c>
       <c r="F56">
-        <v>-5.801024350193887</v>
+        <v>-5.115407968987757</v>
       </c>
       <c r="G56">
-        <v>-6.439578327838008</v>
+        <v>-5.970245597281071</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.622994513818336</v>
       </c>
       <c r="E57">
-        <v>-16.9240143910296</v>
+        <v>-14.29557939360154</v>
       </c>
       <c r="F57">
-        <v>-5.644696739280859</v>
+        <v>-5.085862351429319</v>
       </c>
       <c r="G57">
-        <v>-7.297694905435875</v>
+        <v>-5.357718529968499</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.493334902030723</v>
       </c>
       <c r="E58">
-        <v>-17.14758515278828</v>
+        <v>-14.07206297353095</v>
       </c>
       <c r="F58">
-        <v>-5.944837516963113</v>
+        <v>-5.394739642794094</v>
       </c>
       <c r="G58">
-        <v>-6.945413133510949</v>
+        <v>-6.185642932248212</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.382937731345134</v>
       </c>
       <c r="E59">
-        <v>-15.45889908143198</v>
+        <v>-14.04131010654486</v>
       </c>
       <c r="F59">
-        <v>-5.93504229587612</v>
+        <v>-5.300535271973051</v>
       </c>
       <c r="G59">
-        <v>-7.504974782740722</v>
+        <v>-5.995932120120276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.296349292482964</v>
       </c>
       <c r="E60">
-        <v>-15.07711702326731</v>
+        <v>-13.21208311710431</v>
       </c>
       <c r="F60">
-        <v>-6.017280976653059</v>
+        <v>-5.715778211883529</v>
       </c>
       <c r="G60">
-        <v>-7.598573836772537</v>
+        <v>-5.380869174924622</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.234269558877422</v>
       </c>
       <c r="E61">
-        <v>-15.14083265255523</v>
+        <v>-13.64600149651928</v>
       </c>
       <c r="F61">
-        <v>-6.274144218710577</v>
+        <v>-5.743612635200335</v>
       </c>
       <c r="G61">
-        <v>-7.50925200757746</v>
+        <v>-7.273839114279887</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.194105169925147</v>
       </c>
       <c r="E62">
-        <v>-13.92116969112136</v>
+        <v>-13.37513535222449</v>
       </c>
       <c r="F62">
-        <v>-5.922754321678225</v>
+        <v>-5.583123836994489</v>
       </c>
       <c r="G62">
-        <v>-7.877123138446814</v>
+        <v>-6.917376123338862</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.175383398740628</v>
       </c>
       <c r="E63">
-        <v>-15.43574046535675</v>
+        <v>-12.3615089011916</v>
       </c>
       <c r="F63">
-        <v>-5.976201228912475</v>
+        <v>-5.807801027806053</v>
       </c>
       <c r="G63">
-        <v>-7.777793530086521</v>
+        <v>-7.606770747527772</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.176186371860299</v>
       </c>
       <c r="E64">
-        <v>-13.28840601802958</v>
+        <v>-11.7208203985864</v>
       </c>
       <c r="F64">
-        <v>-6.08315284864689</v>
+        <v>-5.887968221245598</v>
       </c>
       <c r="G64">
-        <v>-8.588135625007165</v>
+        <v>-7.532975376911878</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.190566274790131</v>
       </c>
       <c r="E65">
-        <v>-13.48838343020831</v>
+        <v>-11.97338245094219</v>
       </c>
       <c r="F65">
-        <v>-5.882452173542122</v>
+        <v>-5.821606984123896</v>
       </c>
       <c r="G65">
-        <v>-7.945856684933163</v>
+        <v>-7.563392669326702</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.211504246415841</v>
       </c>
       <c r="E66">
-        <v>-13.02987543693168</v>
+        <v>-12.16790305194167</v>
       </c>
       <c r="F66">
-        <v>-6.255660786971484</v>
+        <v>-5.74578785527519</v>
       </c>
       <c r="G66">
-        <v>-8.39338616256846</v>
+        <v>-7.295324554829756</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.230029263676511</v>
       </c>
       <c r="E67">
-        <v>-13.88472906078164</v>
+        <v>-11.42159242158156</v>
       </c>
       <c r="F67">
-        <v>-6.295753885926749</v>
+        <v>-6.025448148058981</v>
       </c>
       <c r="G67">
-        <v>-9.295221804557942</v>
+        <v>-8.330849957331626</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.232655488887507</v>
       </c>
       <c r="E68">
-        <v>-12.46665101070169</v>
+        <v>-11.27943909400678</v>
       </c>
       <c r="F68">
-        <v>-5.984826091327959</v>
+        <v>-6.349423303842118</v>
       </c>
       <c r="G68">
-        <v>-9.199192810100302</v>
+        <v>-8.080357529102672</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.203931936061434</v>
       </c>
       <c r="E69">
-        <v>-12.32465617971718</v>
+        <v>-11.40271774191759</v>
       </c>
       <c r="F69">
-        <v>-6.211391059590726</v>
+        <v>-6.000260889179832</v>
       </c>
       <c r="G69">
-        <v>-9.409094639472253</v>
+        <v>-8.777654425493823</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.130944680660882</v>
       </c>
       <c r="E70">
-        <v>-13.08200270123398</v>
+        <v>-11.61357707713675</v>
       </c>
       <c r="F70">
-        <v>-6.427305605572164</v>
+        <v>-5.60656030898412</v>
       </c>
       <c r="G70">
-        <v>-9.288269658925472</v>
+        <v>-8.430871469709627</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.002793324305807</v>
       </c>
       <c r="E71">
-        <v>-12.85826891441102</v>
+        <v>-11.28943343614171</v>
       </c>
       <c r="F71">
-        <v>-6.87941365585576</v>
+        <v>-5.632765098913939</v>
       </c>
       <c r="G71">
-        <v>-9.559125252766483</v>
+        <v>-8.074011213303889</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.812566109054631</v>
       </c>
       <c r="E72">
-        <v>-12.61380830205495</v>
+        <v>-10.94828084677386</v>
       </c>
       <c r="F72">
-        <v>-6.431759778459337</v>
+        <v>-5.968939937290186</v>
       </c>
       <c r="G72">
-        <v>-9.675735908841771</v>
+        <v>-8.472882292602979</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.562382993691567</v>
       </c>
       <c r="E73">
-        <v>-13.40776753592376</v>
+        <v>-11.73688742436561</v>
       </c>
       <c r="F73">
-        <v>-6.512606777663084</v>
+        <v>-5.84504266426057</v>
       </c>
       <c r="G73">
-        <v>-8.916061713399673</v>
+        <v>-8.35204406987404</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.261279886501956</v>
       </c>
       <c r="E74">
-        <v>-13.34168351472982</v>
+        <v>-12.54856204855243</v>
       </c>
       <c r="F74">
-        <v>-6.677803141702573</v>
+        <v>-5.950682975497</v>
       </c>
       <c r="G74">
-        <v>-9.974214694662463</v>
+        <v>-8.420016190886356</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.922241821647083</v>
       </c>
       <c r="E75">
-        <v>-13.12631381939903</v>
+        <v>-11.96013666446975</v>
       </c>
       <c r="F75">
-        <v>-6.500981980317279</v>
+        <v>-6.227978795349039</v>
       </c>
       <c r="G75">
-        <v>-8.954288582741638</v>
+        <v>-7.876805326075044</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.559344847455151</v>
       </c>
       <c r="E76">
-        <v>-13.69329687905539</v>
+        <v>-13.3009317771348</v>
       </c>
       <c r="F76">
-        <v>-6.548983314761291</v>
+        <v>-6.451045357244601</v>
       </c>
       <c r="G76">
-        <v>-9.420605406312298</v>
+        <v>-8.344267598402293</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.187096221632777</v>
       </c>
       <c r="E77">
-        <v>-13.21994454798162</v>
+        <v>-13.912687859305</v>
       </c>
       <c r="F77">
-        <v>-7.009258932377289</v>
+        <v>-6.077901279831293</v>
       </c>
       <c r="G77">
-        <v>-9.223399519083452</v>
+        <v>-8.119925169388042</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.8165861263971448</v>
       </c>
       <c r="E78">
-        <v>-15.08788573445755</v>
+        <v>-13.07306349354283</v>
       </c>
       <c r="F78">
-        <v>-6.547020311279105</v>
+        <v>-6.596307614926453</v>
       </c>
       <c r="G78">
-        <v>-9.080930191800917</v>
+        <v>-7.889779354043448</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.4551041995127721</v>
       </c>
       <c r="E79">
-        <v>-15.14008092586996</v>
+        <v>-13.4216654226533</v>
       </c>
       <c r="F79">
-        <v>-7.192677020753345</v>
+        <v>-6.079342452214343</v>
       </c>
       <c r="G79">
-        <v>-9.187053039607795</v>
+        <v>-7.552385105408625</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1086465262675681</v>
       </c>
       <c r="E80">
-        <v>-15.4963993746895</v>
+        <v>-14.44193061658143</v>
       </c>
       <c r="F80">
-        <v>-6.97361921445624</v>
+        <v>-6.254684036348137</v>
       </c>
       <c r="G80">
-        <v>-9.140188956953871</v>
+        <v>-7.078109730361557</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.2235097152000886</v>
       </c>
       <c r="E81">
-        <v>-15.60671752999035</v>
+        <v>-15.83398805501331</v>
       </c>
       <c r="F81">
-        <v>-7.038654097873761</v>
+        <v>-6.649713345806902</v>
       </c>
       <c r="G81">
-        <v>-9.033519869133015</v>
+        <v>-7.533558032926789</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.5457862255268002</v>
       </c>
       <c r="E82">
-        <v>-17.0592708526907</v>
+        <v>-16.64986963155325</v>
       </c>
       <c r="F82">
-        <v>-7.143038134392769</v>
+        <v>-6.395738783339145</v>
       </c>
       <c r="G82">
-        <v>-8.480797806987376</v>
+        <v>-7.417192357221407</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8637421794006712</v>
       </c>
       <c r="E83">
-        <v>-18.28430911277167</v>
+        <v>-16.49603284103868</v>
       </c>
       <c r="F83">
-        <v>-7.246660804292929</v>
+        <v>-6.4030887624927</v>
       </c>
       <c r="G83">
-        <v>-8.969156242758505</v>
+        <v>-7.622475975566075</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.180899242558308</v>
       </c>
       <c r="E84">
-        <v>-19.25306291486256</v>
+        <v>-17.71758417613375</v>
       </c>
       <c r="F84">
-        <v>-7.202199448496404</v>
+        <v>-6.597629217512887</v>
       </c>
       <c r="G84">
-        <v>-8.32883714564375</v>
+        <v>-6.661586822247073</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.498493997440247</v>
       </c>
       <c r="E85">
-        <v>-19.87072412713875</v>
+        <v>-18.1494783276673</v>
       </c>
       <c r="F85">
-        <v>-7.293915817324291</v>
+        <v>-6.961782200517766</v>
       </c>
       <c r="G85">
-        <v>-8.560406495570231</v>
+        <v>-6.062785276740319</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.814385566238969</v>
       </c>
       <c r="E86">
-        <v>-20.51091449760311</v>
+        <v>-20.88752050997701</v>
       </c>
       <c r="F86">
-        <v>-7.374476561683823</v>
+        <v>-7.171401119558853</v>
       </c>
       <c r="G86">
-        <v>-8.312529398317301</v>
+        <v>-7.127721565813074</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.121820639575196</v>
       </c>
       <c r="E87">
-        <v>-21.9695178615777</v>
+        <v>-21.51294352670235</v>
       </c>
       <c r="F87">
-        <v>-7.432465933410032</v>
+        <v>-6.683504878924634</v>
       </c>
       <c r="G87">
-        <v>-8.435920051657016</v>
+        <v>-6.924228952605152</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.412879667721616</v>
       </c>
       <c r="E88">
-        <v>-24.32015814947923</v>
+        <v>-22.91368204980694</v>
       </c>
       <c r="F88">
-        <v>-7.454266041262534</v>
+        <v>-7.009452144498972</v>
       </c>
       <c r="G88">
-        <v>-8.702342825020944</v>
+        <v>-6.885051956693418</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.675164329115764</v>
       </c>
       <c r="E89">
-        <v>-25.1862967305563</v>
+        <v>-24.4102883676539</v>
       </c>
       <c r="F89">
-        <v>-7.594140531420062</v>
+        <v>-6.772441052017967</v>
       </c>
       <c r="G89">
-        <v>-8.309857788067108</v>
+        <v>-7.442044622584716</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.893210378840681</v>
       </c>
       <c r="E90">
-        <v>-26.04637621341111</v>
+        <v>-26.06093978581978</v>
       </c>
       <c r="F90">
-        <v>-7.236639905112987</v>
+        <v>-6.884375010562354</v>
       </c>
       <c r="G90">
-        <v>-8.763693854954717</v>
+        <v>-6.248102994937641</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.049879436721217</v>
       </c>
       <c r="E91">
-        <v>-28.73076956415196</v>
+        <v>-27.98775113439542</v>
       </c>
       <c r="F91">
-        <v>-7.203613697878891</v>
+        <v>-7.004854646226452</v>
       </c>
       <c r="G91">
-        <v>-8.690626804357462</v>
+        <v>-6.366018005955402</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.12722298597135</v>
       </c>
       <c r="E92">
-        <v>-30.35900730021687</v>
+        <v>-30.09291190328916</v>
       </c>
       <c r="F92">
-        <v>-7.378381584544817</v>
+        <v>-7.102398260970198</v>
       </c>
       <c r="G92">
-        <v>-8.657594180966614</v>
+        <v>-6.721355411413075</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.108057030724726</v>
       </c>
       <c r="E93">
-        <v>-32.28534089478471</v>
+        <v>-32.38053621113695</v>
       </c>
       <c r="F93">
-        <v>-7.341186667414807</v>
+        <v>-6.961336783229049</v>
       </c>
       <c r="G93">
-        <v>-9.263609405203441</v>
+        <v>-7.024329918076096</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.978596735450535</v>
       </c>
       <c r="E94">
-        <v>-34.13098161100987</v>
+        <v>-33.60235472619848</v>
       </c>
       <c r="F94">
-        <v>-7.241327674622688</v>
+        <v>-6.370100564200575</v>
       </c>
       <c r="G94">
-        <v>-9.932879223059121</v>
+        <v>-6.662768687004593</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.731223993134446</v>
       </c>
       <c r="E95">
-        <v>-35.33666064470805</v>
+        <v>-35.98089947093527</v>
       </c>
       <c r="F95">
-        <v>-7.028086028300033</v>
+        <v>-6.577015305391049</v>
       </c>
       <c r="G95">
-        <v>-10.04838415692429</v>
+        <v>-7.013987773811412</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.356767511847649</v>
       </c>
       <c r="E96">
-        <v>-38.59464409868244</v>
+        <v>-38.26914417972211</v>
       </c>
       <c r="F96">
-        <v>-6.318295564074156</v>
+        <v>-6.201654039696126</v>
       </c>
       <c r="G96">
-        <v>-9.691513968881939</v>
+        <v>-7.861520537320229</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.867446486827971</v>
       </c>
       <c r="E97">
-        <v>-40.48419742735999</v>
+        <v>-40.12801256852367</v>
       </c>
       <c r="F97">
-        <v>-6.879931527690109</v>
+        <v>-6.422005733726145</v>
       </c>
       <c r="G97">
-        <v>-10.65006256650467</v>
+        <v>-8.300190995092436</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.257000377632133</v>
       </c>
       <c r="E98">
-        <v>-43.53795349629946</v>
+        <v>-42.31886112259055</v>
       </c>
       <c r="F98">
-        <v>-6.113522785134315</v>
+        <v>-6.403104995478333</v>
       </c>
       <c r="G98">
-        <v>-10.08284031489703</v>
+        <v>-8.558473136975296</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.5706422346465799</v>
       </c>
       <c r="E99">
-        <v>-45.69759860021647</v>
+        <v>-44.58754961637527</v>
       </c>
       <c r="F99">
-        <v>-6.015614918030018</v>
+        <v>-5.940299407662421</v>
       </c>
       <c r="G99">
-        <v>-11.00625078216594</v>
+        <v>-9.546233988436562</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.2050830126873504</v>
       </c>
       <c r="E100">
-        <v>-47.93279676447747</v>
+        <v>-46.75311796429432</v>
       </c>
       <c r="F100">
-        <v>-5.729953171679669</v>
+        <v>-5.828298933469585</v>
       </c>
       <c r="G100">
-        <v>-11.31452216169179</v>
+        <v>-8.988880473081482</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.9670524041445185</v>
       </c>
       <c r="E101">
-        <v>-50.99720720063848</v>
+        <v>-50.9514016860509</v>
       </c>
       <c r="F101">
-        <v>-5.611086540490446</v>
+        <v>-5.523816426020155</v>
       </c>
       <c r="G101">
-        <v>-11.42423695140878</v>
+        <v>-8.884532077683653</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.786470978206226</v>
       </c>
       <c r="E102">
-        <v>-52.28058126288627</v>
+        <v>-52.55750310904782</v>
       </c>
       <c r="F102">
-        <v>-4.947952448459894</v>
+        <v>-5.431703338860451</v>
       </c>
       <c r="G102">
-        <v>-12.17678023175929</v>
+        <v>-10.09370552535692</v>
       </c>
     </row>
   </sheetData>
